--- a/test-cases/test-cases.xlsx
+++ b/test-cases/test-cases.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aai06\Downloads\Library-Management-v2\Library-Management-v2\test-cases\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DCB5DB0-705B-4611-B82A-012269FF4566}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,29 +24,1009 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="294">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Feature / Module</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ขั้นตอนการทดสอบ </t>
+  </si>
+  <si>
+    <t>(Test Steps)</t>
+  </si>
+  <si>
+    <t>ผลลัพธ์ที่คาดหวัง (Expected Result)</t>
+  </si>
+  <si>
+    <t>ผลการทดสอบจริง</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (Actual Result)</t>
+  </si>
+  <si>
+    <t>สถานะ (Pass/Fail)</t>
+  </si>
+  <si>
+    <t>TC-01</t>
+  </si>
+  <si>
+    <t>Login</t>
+  </si>
+  <si>
+    <t>1. เข้าหน้า login.html</t>
+  </si>
+  <si>
+    <t>2. กรอก Username: admin</t>
+  </si>
+  <si>
+    <t>3. กรอก Password: admin123</t>
+  </si>
+  <si>
+    <t>4. กดปุ่ม Login</t>
+  </si>
+  <si>
+    <t>ระบบตรวจสอบสิทธิ์ผ่าน และนำผู้ใช้ไปยังหน้า dashboard.html</t>
+  </si>
+  <si>
+    <t>ระบบอนุญาตให้เข้าสู่ระบบ และแสดงข้อความแจ้งเตือน</t>
+  </si>
+  <si>
+    <t>ผ่าน</t>
+  </si>
+  <si>
+    <t>TC-02</t>
+  </si>
+  <si>
+    <t>2. กรอก Username: librarian</t>
+  </si>
+  <si>
+    <t>3. กรอก Password: lib123</t>
+  </si>
+  <si>
+    <t>TC-03</t>
+  </si>
+  <si>
+    <t>Login (Negative)</t>
+  </si>
+  <si>
+    <t>1. กรอก Username ที่มีในระบบ</t>
+  </si>
+  <si>
+    <t>2. กรอก Password ที่ "ผิด"</t>
+  </si>
+  <si>
+    <t>3. กดปุ่ม Login</t>
+  </si>
+  <si>
+    <t>ระบบไม่อนุญาตให้เข้าสู่ระบบ และแสดงข้อความแจ้งเตือนความผิดพลาด</t>
+  </si>
+  <si>
+    <t>ระบบไม่อนุญาตให้เข้าสู่ระบบ และแสดงข้อความแจ้งเตือน</t>
+  </si>
+  <si>
+    <t>TC-04</t>
+  </si>
+  <si>
+    <t>1. กรอก Username ที่ "ไม่มี" ในระบบ</t>
+  </si>
+  <si>
+    <t>2. กดปุ่ม Login</t>
+  </si>
+  <si>
+    <t>ระบบไม่อนุญาตให้เข้าสู่ระบบ และแสดงข้อความแจ้งเตือน "User not found"</t>
+  </si>
+  <si>
+    <t>TC-05</t>
+  </si>
+  <si>
+    <t>Login (Empty)</t>
+  </si>
+  <si>
+    <t>1. ไม่กรอก Username และ Password</t>
+  </si>
+  <si>
+    <t>ระบบต้องมีการแจ้งเตือนให้กรอกข้อมูลให้ครบถ้วน (Validation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ระบบมีการแจ้งเตือนให้กรอกข้อมูลให้ครบถ้วน  </t>
+  </si>
+  <si>
+    <t>TC-06</t>
+  </si>
+  <si>
+    <t>Dashboard</t>
+  </si>
+  <si>
+    <t>1. ล็อกอินเข้าสู่ระบบ</t>
+  </si>
+  <si>
+    <t>2. ตรวจสอบการแสดงผลการ์ดสถิติ (Total Books, Members, etc.)</t>
+  </si>
+  <si>
+    <t>ตัวเลขสถิติต้องแสดงผลเป็นจำนวนที่ถูกต้อง (ไม่เป็นค่าว่าง หรือ NaN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ตัวเลขสถิติแสดงผลเป็นจำนวนที่ถูกต้อง  </t>
+  </si>
+  <si>
+    <t>TC-07</t>
+  </si>
+  <si>
+    <t>1. ตรวจสอบชื่อผู้ใช้งานและบทบาท (Role) ที่มุมขวาบนของหน้าจอ</t>
+  </si>
+  <si>
+    <t>ชื่อและบทบาทต้องตรงกับบัญชีที่ใช้ล็อกอินเข้ามาจริง</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ชื่อและบทบาทตรงกับบัญชีที่ใช้ล็อกอินเข้ามา  </t>
+  </si>
+  <si>
+    <t>TC-08</t>
+  </si>
+  <si>
+    <t>Navigation</t>
+  </si>
+  <si>
+    <t>1. คลิกเมนูต่างๆ บน Sidebar (Books, Members, Borrowing, Reports)</t>
+  </si>
+  <si>
+    <t>ระบบต้องนำทางไปยังหน้าเพจที่ถูกต้องทุกเมนู โดยไม่เกิด Error 404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ระบบนำทางไปยังหน้าเพจที่ถูกต้องทุกเมนูและไม่เกิด Error 404  </t>
+  </si>
+  <si>
+    <t>TC-09</t>
+  </si>
+  <si>
+    <t>Session Logout</t>
+  </si>
+  <si>
+    <t>1. กดปุ่ม Logout</t>
+  </si>
+  <si>
+    <t>2. พยายามกดปุ่ม Back บน Browser หรือพิมพ์ URL หน้า Dashboard โดยตรง</t>
+  </si>
+  <si>
+    <t>ระบบต้องไม่อนุญาตให้เข้าถึงหน้าภายใน และผลักผู้ใช้กลับไปหน้า Login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ระบบไม่อนุญาตให้เข้าถึงหน้าภายใน และผลักผู้ใช้กลับไปหน้า Login  </t>
+  </si>
+  <si>
+    <t>TC-10</t>
+  </si>
+  <si>
+    <t>UI Layout</t>
+  </si>
+  <si>
+    <t>1. ลองย่อ-ขยายหน้าจอ Browser (Responsive Test)</t>
+  </si>
+  <si>
+    <t>หน้าจอ Dashboard และเมนู Sidebar ต้องปรับขนาดตามหน้าจอได้อย่างเหมาะสม</t>
+  </si>
+  <si>
+    <t xml:space="preserve">หน้าจอ Dashboard และ เมนู Sidebar ปรับขนาดตามหน้าจอ  </t>
+  </si>
+  <si>
+    <t>TC-11</t>
+  </si>
+  <si>
+    <t>Add Book</t>
+  </si>
+  <si>
+    <t>1. ไปหน้า books.html</t>
+  </si>
+  <si>
+    <t>2. คลิกปุ่ม "+ Add Book"</t>
+  </si>
+  <si>
+    <t>3. กรอกข้อมูลครบถ้วน (ISBN, Title, Author)</t>
+  </si>
+  <si>
+    <t>4. กด Save</t>
+  </si>
+  <si>
+    <t>ข้อมูลหนังสือใหม่ต้องปรากฏในตาราง และมีข้อความแจ้งเตือนว่าบันทึกสำเร็จ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ข้อมูลหนังสือใหม่ปรากฏในตาราง และมีข้อความแจ้งเตือนว่าบันทึกสำเร็จ  </t>
+  </si>
+  <si>
+    <t>TC-12</t>
+  </si>
+  <si>
+    <t>Add Book (Negative)</t>
+  </si>
+  <si>
+    <t>1. คลิก "+ Add Book"</t>
+  </si>
+  <si>
+    <t>2. กรอกข้อมูล "ไม่ครบ" (เช่น ไม่ใส่ชื่อหนังสือ)</t>
+  </si>
+  <si>
+    <t>3. กด Save</t>
+  </si>
+  <si>
+    <t>ระบบต้องไม่อนุญาตให้บันทึก และแสดงข้อความเตือนให้กรอกข้อมูลที่จำเป็น</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ระบบไม่อนุญาตให้บันทึก และแสดงข้อความเตือนให้หรอกข้อมูลที่จำเป็น  </t>
+  </si>
+  <si>
+    <t>TC-13</t>
+  </si>
+  <si>
+    <t>Add Book (Duplicate)</t>
+  </si>
+  <si>
+    <t>1. ลองเพิ่มหนังสือโดยใช้ ISBN ที่มีอยู่แล้ว ในระบบ</t>
+  </si>
+  <si>
+    <t>2. กด Save</t>
+  </si>
+  <si>
+    <t>ระบบต้องป้องกันการบันทึกข้อมูลซ้ำ (Unique Constraint) และแจ้งเตือนผู้ใช้</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ระบบป้องกันการบันทึกข้อมูลซ้ำ และแจ้งเตือนผู้ใช้  </t>
+  </si>
+  <si>
+    <t>TC-14</t>
+  </si>
+  <si>
+    <t>Search Book</t>
+  </si>
+  <si>
+    <t>1. พิมพ์ชื่อหนังสือที่มีอยู่ในระบบลงในช่อง Search</t>
+  </si>
+  <si>
+    <t>2. กดปุ่ม Search หรือ Enter</t>
+  </si>
+  <si>
+    <t>ตารางต้องแสดงเฉพาะรายชื่อหนังสือที่ตรงกับคำค้นหา</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ตารางแสดงเฉพาะรายชื่อหนังสือที่ตรงกับคำค้นหา  </t>
+  </si>
+  <si>
+    <t>TC-15</t>
+  </si>
+  <si>
+    <t>Search Book (ISBN)</t>
+  </si>
+  <si>
+    <t>1. พิมพ์เลข ISBN ของหนังสือลงในช่อง Search</t>
+  </si>
+  <si>
+    <t>ระบบต้องค้นหาและแสดงผลหนังสือเล่มนั้นได้อย่างแม่นยำ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ระบบค้นหาและแสดงผลหนังสือเล่มตามเลขที่ค้นหา  </t>
+  </si>
+  <si>
+    <t>TC-16</t>
+  </si>
+  <si>
+    <t>Search (Not Found)</t>
+  </si>
+  <si>
+    <t>1. พิมพ์ชื่อหนังสือที่ "ไม่มี" ในระบบลงในช่อง Search</t>
+  </si>
+  <si>
+    <t>ระบบต้องแสดงข้อความว่า "No books found" หรือตารางว่างเปล่า</t>
+  </si>
+  <si>
+    <t>ระบบแสดงข้อความว่า "No books found"</t>
+  </si>
+  <si>
+    <t>TC-17</t>
+  </si>
+  <si>
+    <t>Search (Security)</t>
+  </si>
+  <si>
+    <t>1. ลองใส่ Payload ในช่อง Search เช่น ' OR '1'='1</t>
+  </si>
+  <si>
+    <t>(เพื่อทดสอบ SQL Injection)</t>
+  </si>
+  <si>
+    <t>ระบบต้องจัดการข้อมูลให้ปลอดภัย ไม่แสดงข้อมูลหนังสือทั้งหมดออกมาโดยมิชอบ</t>
+  </si>
+  <si>
+    <t>ระบบไม่แสดงข้อมูลหนังสือทั้งหมดออกมา</t>
+  </si>
+  <si>
+    <t>TC-18</t>
+  </si>
+  <si>
+    <t>Edit Book</t>
+  </si>
+  <si>
+    <t>1. คลิกปุ่ม "Edit" ที่หนังสือเล่มใดเล่มหนึ่ง</t>
+  </si>
+  <si>
+    <t>2. แก้ไขชื่อหนังสือ หรือจำนวนเล่ม</t>
+  </si>
+  <si>
+    <t>3. กด Update</t>
+  </si>
+  <si>
+    <t>ข้อมูลในตารางต้องเปลี่ยนตามที่แก้ไขจริง และบันทึกลงฐานข้อมูลสำเร็จ</t>
+  </si>
+  <si>
+    <t>ข้อมูลเปลี่ยนตามที่แก้ไข และ บันทึกลงฐานข้อมูลสำเร็จ</t>
+  </si>
+  <si>
+    <t>TC-19</t>
+  </si>
+  <si>
+    <t>Delete Book</t>
+  </si>
+  <si>
+    <t>1. คลิกปุ่ม "Delete" ที่หนังสือที่ไม่ได้ถูกยืมอยู่</t>
+  </si>
+  <si>
+    <t>2. กดยืนยันการลบ (Confirm)</t>
+  </si>
+  <si>
+    <t>ข้อมูลหนังสือเล่มนั้นต้องถูกลบออกจากตารางและฐานข้อมูลทันที</t>
+  </si>
+  <si>
+    <t>ข้อมูลหนังสือถูกลบออกจากตารางและฐานข้อมูล</t>
+  </si>
+  <si>
+    <t>TC-20</t>
+  </si>
+  <si>
+    <t>Delete (Logic Bug)</t>
+  </si>
+  <si>
+    <t>1. ลองลบหนังสือที่ "กำลังถูกยืมอยู่" (Status: Borrowed)</t>
+  </si>
+  <si>
+    <t>ระบบควรไม่อนุญาตให้ลบหนังสือที่ติดรายการยืม เพื่อรักษาความถูกต้องของข้อมูล</t>
+  </si>
+  <si>
+    <t>ระบบไม่อนุญาตให้ลบหนังสือที่ติดรายการยืม</t>
+  </si>
+  <si>
+    <t>TC-21</t>
+  </si>
+  <si>
+    <t>Add Member</t>
+  </si>
+  <si>
+    <t>1. ไปหน้า members.html</t>
+  </si>
+  <si>
+    <t>2. คลิกปุ่ม "+ Add Member"</t>
+  </si>
+  <si>
+    <t>3. กรอกข้อมูลครบถ้วน (Code, Name, Type)</t>
+  </si>
+  <si>
+    <t>ข้อมูลสมาชิกใหม่ต้องปรากฏในตาราง และมีสถานะเริ่มต้นเป็น "Active"</t>
+  </si>
+  <si>
+    <t>ข้อมูลสมาชิกใหม่ปรากฏในตาราง และมีสถานะเริ่มต้นเป็น Active</t>
+  </si>
+  <si>
+    <t>TC-22</t>
+  </si>
+  <si>
+    <t>Add Member (Validation)</t>
+  </si>
+  <si>
+    <t>1. คลิก "+ Add Member"</t>
+  </si>
+  <si>
+    <t>2. ไม่กรอกชื่อสมาชิก (Full Name)</t>
+  </si>
+  <si>
+    <t>ระบบต้องแจ้งเตือนว่าจำเป็นต้องกรอกชื่อ และไม่อนุญาตให้บันทึกค่าว่าง</t>
+  </si>
+  <si>
+    <t>ระบบแจ้งเตือนว่าจำเป็นต้องกรอกชื่อ และไม่อนุญาตให้บันทึกค่าว่าง</t>
+  </si>
+  <si>
+    <t>TC-23</t>
+  </si>
+  <si>
+    <t>Duplicate Code (Bug)</t>
+  </si>
+  <si>
+    <t>1. ลองเพิ่มสมาชิกโดยใช้ Member Code ที่ซ้ำ กับคนที่มีอยู่แล้ว</t>
+  </si>
+  <si>
+    <t>ระบบต้องป้องกันไม่ให้ใช้รหัสซ้ำกัน (ตามกฎ Unique Key ในฐานข้อมูล)</t>
+  </si>
+  <si>
+    <t>ระบบป้องกันไม่ให้ใช้รหัสซ้ำกัน</t>
+  </si>
+  <si>
+    <t>TC-24</t>
+  </si>
+  <si>
+    <t>Member Type Logic</t>
+  </si>
+  <si>
+    <t>1. เพิ่มสมาชิกประเภท "Student"</t>
+  </si>
+  <si>
+    <t>2. ตรวจสอบค่า Max Books ในฐานข้อมูล</t>
+  </si>
+  <si>
+    <t>ระบบควรตั้งค่าจำนวนหนังสือสูงสุดที่ยืมได้ตามประเภท (เช่น Student = 3 เล่ม)</t>
+  </si>
+  <si>
+    <t>ระบบยอมให้ผู้ใช้กรอกค่า Max Books ของ Student เกิน 3 เล่ม และบันทึกลงฐานข้อมูลได้</t>
+  </si>
+  <si>
+    <t>ไม่ผ่าน</t>
+  </si>
+  <si>
+    <t>TC-25</t>
+  </si>
+  <si>
+    <t>Edit Member</t>
+  </si>
+  <si>
+    <t>1. คลิกปุ่ม "Edit" ที่สมาชิกคนใดคนหนึ่ง</t>
+  </si>
+  <si>
+    <t>2. แก้ไขเบอร์โทรศัพท์หรืออีเมล</t>
+  </si>
+  <si>
+    <t>ข้อมูลในตารางต้องเปลี่ยนตามจริง และระบบแจ้งว่าแก้ไขสำเร็จ</t>
+  </si>
+  <si>
+    <t>ข้อมูลในตารางเปลี่ยนตามจริง และระบบแจ้งว่าแก้ไขสำเร็จ</t>
+  </si>
+  <si>
+    <t>TC-26</t>
+  </si>
+  <si>
+    <t>Modal Inconsistency</t>
+  </si>
+  <si>
+    <t>1. เปิดหน้า Add Member</t>
+  </si>
+  <si>
+    <t>2. เปิดหน้า Edit Member</t>
+  </si>
+  <si>
+    <t>3. เปรียบเทียบตัวเลือก "Member Type"</t>
+  </si>
+  <si>
+    <t>ตัวเลือกประเภทสมาชิกในทั้งสองหน้าต้อง "ตรงกัน" (ถ้าไม่ตรงกันคือ UI Bug)</t>
+  </si>
+  <si>
+    <t>ตัวเลือกประเภทสมาชิกของทั้งสองหน้าตรงกัน</t>
+  </si>
+  <si>
+    <t>TC-27</t>
+  </si>
+  <si>
+    <t>Suspended Status</t>
+  </si>
+  <si>
+    <t>1. คลิกปุ่ม "Edit" สมาชิก</t>
+  </si>
+  <si>
+    <t>2. เปลี่ยนสถานะ (Status) เป็น "Suspended"</t>
+  </si>
+  <si>
+    <t>สถานะในตารางต้องเปลี่ยนเป็น Suspended เพื่อเตรียมบล็อกการยืมหนังสือ</t>
+  </si>
+  <si>
+    <t>สถานะเปลี่ยนเป็น Suspended เพื่อเตรียมบล็อกการยืมหนังสือ</t>
+  </si>
+  <si>
+    <t>TC-28</t>
+  </si>
+  <si>
+    <t>Search Member</t>
+  </si>
+  <si>
+    <t>1. พิมพ์ชื่อหรือรหัสสมาชิกในช่อง Search</t>
+  </si>
+  <si>
+    <t>2. กดปุ่ม Search</t>
+  </si>
+  <si>
+    <t>ระบบต้องกรองข้อมูลสมาชิกที่ตรงตามคำค้นหามาแสดงผล</t>
+  </si>
+  <si>
+    <t>ไม่มีช่อง Search ปรากฏอยู่ในหน้า Member</t>
+  </si>
+  <si>
+    <t>TC-29</t>
+  </si>
+  <si>
+    <t>Delete Member</t>
+  </si>
+  <si>
+    <t>1. คลิกปุ่ม "Delete" สมาชิกที่ไม่มีประวัติค้างส่ง</t>
+  </si>
+  <si>
+    <t>2. กดยืนยันการลบ</t>
+  </si>
+  <si>
+    <t>ข้อมูลสมาชิกต้องถูกลบออกจากตารางและฐานข้อมูลทันที</t>
+  </si>
+  <si>
+    <t>ข้อมูลสมาชิกถูกลบออกจากตารางและฐานข้อมูล</t>
+  </si>
+  <si>
+    <t>TC-30</t>
+  </si>
+  <si>
+    <t>Delete (Safety Check)</t>
+  </si>
+  <si>
+    <t>1. ลองลบสมาชิกที่ "ยังคืนหนังสือไม่ครบ" (มีรายการยืมที่ยังไม่คืน)</t>
+  </si>
+  <si>
+    <t>ระบบควรไม่อนุญาตให้ลบสมาชิกที่มีภาระผูกพัน เพื่อป้องกันข้อมูลสูญหาย</t>
+  </si>
+  <si>
+    <t>ระบบไม่อนุญาตให้ลบสมาชิก</t>
+  </si>
+  <si>
+    <t>TC-31</t>
+  </si>
+  <si>
+    <t>New Borrow</t>
+  </si>
+  <si>
+    <t>1. ไปหน้า borrowing.html</t>
+  </si>
+  <si>
+    <t>2. คลิก "+ New Borrow"</t>
+  </si>
+  <si>
+    <t>3. เลือกสมาชิกและหนังสือที่มีในระบบ</t>
+  </si>
+  <si>
+    <t>ระบบบันทึกรายการยืมสำเร็จ และแสดงในตารางด้วยสถานะ "Borrowed"</t>
+  </si>
+  <si>
+    <t>TC-32</t>
+  </si>
+  <si>
+    <t>Return Book</t>
+  </si>
+  <si>
+    <t>1. ค้นหารายการยืมที่ต้องการคืนในตาราง</t>
+  </si>
+  <si>
+    <t>2. คลิกปุ่ม "Return" (สีเขียว)</t>
+  </si>
+  <si>
+    <t>3. กดยืนยันการคืน</t>
+  </si>
+  <si>
+    <t>สถานะในตารางเปลี่ยนเป็น "Returned" และมีการลงวันที่คืนหนังสือจริง</t>
+  </si>
+  <si>
+    <t>สถานะในตารางเปลี่ยนเป็น "Returned" และมีการลงวันที่คืนหนังสือ</t>
+  </si>
+  <si>
+    <t>TC-33</t>
+  </si>
+  <si>
+    <t>Inventory Sync (Borrow)</t>
+  </si>
+  <si>
+    <t>1. ทำรายการยืมหนังสือเล่ม A</t>
+  </si>
+  <si>
+    <t>2. กลับไปเช็กหน้า books.html</t>
+  </si>
+  <si>
+    <t>จำนวน Available Copies ของหนังสือเล่ม A ต้องลดลง 1 เล่ม</t>
+  </si>
+  <si>
+    <t>จำนวน Avaliable Copies ลดลง 1 เล่ม</t>
+  </si>
+  <si>
+    <t>TC-34</t>
+  </si>
+  <si>
+    <t>Inventory Sync (Return)</t>
+  </si>
+  <si>
+    <t>1. ทำรายการคืนหนังสือเล่ม A</t>
+  </si>
+  <si>
+    <t>จำนวน Available Copies ของหนังสือเล่ม A ต้องเพิ่มกลับมา 1 เล่ม</t>
+  </si>
+  <si>
+    <t>จำนวน Available Copies เพิ่มกลับมา 1 เล่ม</t>
+  </si>
+  <si>
+    <t>TC-35</t>
+  </si>
+  <si>
+    <t>Max Books Limit (Bug)</t>
+  </si>
+  <si>
+    <t>1. เลือกสมาชิกที่มีสิทธิ์ยืมได้ 3 เล่ม</t>
+  </si>
+  <si>
+    <t>2. พยายามทำรายการยืม เล่มที่ 4</t>
+  </si>
+  <si>
+    <t>ระบบต้องไม่อนุญาตให้ยืม และแจ้งเตือนว่าเกินโควตา (เช็ก Bug ที่อาจารย์ฝังไว้)</t>
+  </si>
+  <si>
+    <t>ระบบไม่อนุญาตให้ยืมและแจ้งเตือนว่าเกินโควตา</t>
+  </si>
+  <si>
+    <t>TC-36</t>
+  </si>
+  <si>
+    <t>Out of Stock (Negative)</t>
+  </si>
+  <si>
+    <t>1. พยายามยืมหนังสือที่มียอด Available = 0</t>
+  </si>
+  <si>
+    <t>ระบบต้องไม่อนุญาตให้ทำรายการยืมหนังสือที่ไม่มีในสต็อก</t>
+  </si>
+  <si>
+    <t>ระบบไม่อนุญาตให้ทำรายการยืมหนังสือ</t>
+  </si>
+  <si>
+    <t>TC-37</t>
+  </si>
+  <si>
+    <t>Suspended Member</t>
+  </si>
+  <si>
+    <t>1. พยายามทำรายการยืมให้สมาชิกที่มีสถานะ "Suspended"</t>
+  </si>
+  <si>
+    <t>ระบบต้องไม่อนุญาตให้สมาชิกที่ถูกระงับสิทธิ์ยืมหนังสือได้</t>
+  </si>
+  <si>
+    <t>ระบบไม่อนุญาตให้สมาชิกที่ถูกระงับสิทธิ์ยืมหนังสือ</t>
+  </si>
+  <si>
+    <t>TC-38</t>
+  </si>
+  <si>
+    <t>Date Validation</t>
+  </si>
+  <si>
+    <t>1. ทำรายการยืมโดยเลือก Due Date (วันคืน) มาก่อน Borrow Date (วันยืม)</t>
+  </si>
+  <si>
+    <t>ระบบต้องไม่อนุญาตให้บันทึก และแจ้งเตือนเรื่องความผิดปกติของวันที่</t>
+  </si>
+  <si>
+    <t>ระบบไม่อนุญาตให้บันทึก และแจ้งเตือนเรื่องความผิดปกติของวันที่</t>
+  </si>
+  <si>
+    <t>TC-39</t>
+  </si>
+  <si>
+    <t>Extend Due Date</t>
+  </si>
+  <si>
+    <t>1. คลิกปุ่ม "Extend" (ขยายเวลา) ในรายการยืม</t>
+  </si>
+  <si>
+    <t>2. ระบุวันคืนใหม่</t>
+  </si>
+  <si>
+    <t>ระบบต้องอัปเดต Due Date ใหม่ในฐานข้อมูลและหน้าจอได้อย่างถูกต้อง</t>
+  </si>
+  <si>
+    <t>ไม่พบปุ่ม 'Extend' บนหน้ารายการยืม</t>
+  </si>
+  <si>
+    <t>TC-40</t>
+  </si>
+  <si>
+    <t>Borrow History</t>
+  </si>
+  <si>
+    <t>2. คลิกดูรายละเอียดสมาชิกคนหนึ่ง</t>
+  </si>
+  <si>
+    <t>ระบบต้องแสดงประวัติการยืม-คืนของสมาชิกคนนั้นได้อย่างถูกต้องและครบถ้วน</t>
+  </si>
+  <si>
+    <t>ไม่พบปุ่มให้ดูรายละเอียด</t>
+  </si>
+  <si>
+    <t>TC-41</t>
+  </si>
+  <si>
+    <t>Overdue Logic</t>
+  </si>
+  <si>
+    <t>1. ไปหน้า Reports</t>
+  </si>
+  <si>
+    <t>2. ตรวจสอบรายชื่อในตาราง Overdue</t>
+  </si>
+  <si>
+    <t>ต้องแสดงเฉพาะรายการที่ "เลยกำหนดส่ง" และยังไม่คืนเท่านั้น</t>
+  </si>
+  <si>
+    <t>แสดงรายการที่ "เลยกำหนดส่ง" และยังไม่คืน</t>
+  </si>
+  <si>
+    <t>TC-42</t>
+  </si>
+  <si>
+    <t>Fine Calculation (Bug)</t>
+  </si>
+  <si>
+    <t>1. ดูรายการที่ค้างส่ง 3 วัน</t>
+  </si>
+  <si>
+    <t>2. ตรวจสอบค่า Fine</t>
+  </si>
+  <si>
+    <t>ค่าปรับต้องเท่ากับ 30 บาท (10 บาท x 3 วัน)</t>
+  </si>
+  <si>
+    <t>ระบบสามารถคำนวณและแสดงค่าปรับได้อย่างถูกต้องตามเงื่อนไข</t>
+  </si>
+  <si>
+    <t>TC-43</t>
+  </si>
+  <si>
+    <t>Zero Fine</t>
+  </si>
+  <si>
+    <t>1. ตรวจสอบรายการที่ยังไม่ถึงกำหนดส่ง</t>
+  </si>
+  <si>
+    <t>ค่า Fine ต้องแสดงเป็น 0.00</t>
+  </si>
+  <si>
+    <t>ระบบไม่แสดงข้อมูลหรือคอลัมน์ค่า Fine</t>
+  </si>
+  <si>
+    <t>TC-44</t>
+  </si>
+  <si>
+    <t>Top Borrowed (Bug)</t>
+  </si>
+  <si>
+    <t>1. ตรวจสอบหนังสือ 5 อันดับแรก</t>
+  </si>
+  <si>
+    <t>ข้อมูลต้อง "อัปเดตตามการยืมจริง" ไม่ใช่ข้อมูลนิ่ง (Placeholder)</t>
+  </si>
+  <si>
+    <t>ข้อมูลอัปเดตตามการยืมจริง</t>
+  </si>
+  <si>
+    <t>TC-45</t>
+  </si>
+  <si>
+    <t>Most Active (Bug)</t>
+  </si>
+  <si>
+    <t>1. ตรวจสอบสมาชิก 5 อันดับแรก</t>
+  </si>
+  <si>
+    <t>ต้องแสดงชื่อสมาชิกที่ "มียอดการยืมสูงสุด" จริงจากฐานข้อมูล</t>
+  </si>
+  <si>
+    <t>ระบบสามารถแสดงข้อมูลหนังสือ 5 อันดับแรก โดยดึงข้อมูล และอัปเดตตามสถิติการยืมจริง</t>
+  </si>
+  <si>
+    <t>TC-46</t>
+  </si>
+  <si>
+    <t>Empty Report</t>
+  </si>
+  <si>
+    <t>1. ลบรายการยืมค้างส่งทั้งหมด</t>
+  </si>
+  <si>
+    <t>2. เข้าหน้า Reports</t>
+  </si>
+  <si>
+    <t>ตาราง Overdue ต้องแสดงว่า "No overdue books" (ไม่พัง)</t>
+  </si>
+  <si>
+    <t>ตาราง Overdue แสดงว่า "No overdue books"</t>
+  </si>
+  <si>
+    <t>TC-47</t>
+  </si>
+  <si>
+    <t>Visual: Charts</t>
+  </si>
+  <si>
+    <t>1. ตรวจสอบกราฟหรือสถิติในหน้า Reports</t>
+  </si>
+  <si>
+    <t>กราฟต้องแสดงผลถูกต้อง ไม่เบี้ยว และอ่านข้อมูลง่าย</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ไม่พบการแสดงผลกราฟหรือสถิติใดๆ ในหน้า Reports  </t>
+  </si>
+  <si>
+    <t>TC-48</t>
+  </si>
+  <si>
+    <t>Print/Export (If any)</t>
+  </si>
+  <si>
+    <t>1. ลองกดปุ่ม Print หรือ Export รายงาน (ถ้ามีใน UI)</t>
+  </si>
+  <si>
+    <t>ระบบต้องสร้างไฟล์รายงานที่ข้อมูลครบถ้วน</t>
+  </si>
+  <si>
+    <t>ไม่มีปุ่ม Print หรือ Export ในหน้า UI ตามเงื่อนไข</t>
+  </si>
+  <si>
+    <t>TC-49</t>
+  </si>
+  <si>
+    <t>User Journey E2E</t>
+  </si>
+  <si>
+    <t>1. ยืมหนังสือจน Overdue</t>
+  </si>
+  <si>
+    <t>2. เช็กชื่อในหน้า Reports</t>
+  </si>
+  <si>
+    <t>ชื่อต้องปรากฏในหน้า Reports ทันทีที่ข้อมูลเงื่อนไขตรง</t>
+  </si>
+  <si>
+    <t>ชื่อปรากฏในหน้า Reports ที่ข้อมูลตรงตามเงื่อนไข</t>
+  </si>
+  <si>
+    <t>TC-50</t>
+  </si>
+  <si>
+    <t>Final Summary</t>
+  </si>
+  <si>
+    <t>1. ตรวจสอบยอดรวมทั้งหมดในหน้ารายงาน</t>
+  </si>
+  <si>
+    <t>ยอดรวมหนังสือ/สมาชิก ต้องตรงกับหน้า Dashboard</t>
+  </si>
+  <si>
+    <t>ระบบแสดงยอดรวมของหนังสือ/สมาชิกตรงหน้า Dashboard</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Angsana New"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Angsana New"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Angsana New"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFADADAD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -49,11 +1035,62 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +1367,1757 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B1:G106"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="24.28515625" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="61" customWidth="1"/>
+    <col min="5" max="5" width="78.140625" customWidth="1"/>
+    <col min="6" max="6" width="77.85546875" customWidth="1"/>
+    <col min="7" max="7" width="44.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B2" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="9"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="11"/>
+      <c r="F3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="11"/>
+    </row>
+    <row r="4" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B4" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="12"/>
+    </row>
+    <row r="6" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="12"/>
+    </row>
+    <row r="7" spans="2:7" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="14"/>
+    </row>
+    <row r="8" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B8" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="12"/>
+    </row>
+    <row r="10" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="12"/>
+    </row>
+    <row r="11" spans="2:7" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="14"/>
+    </row>
+    <row r="12" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B12" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="12"/>
+    </row>
+    <row r="14" spans="2:7" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="14"/>
+    </row>
+    <row r="15" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B15" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="14"/>
+    </row>
+    <row r="17" spans="2:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="14"/>
+    </row>
+    <row r="19" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B19" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="14"/>
+    </row>
+    <row r="21" spans="2:7" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="14"/>
+    </row>
+    <row r="25" spans="2:7" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B26" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="12"/>
+    </row>
+    <row r="28" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="12"/>
+    </row>
+    <row r="29" spans="2:7" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="14"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="14"/>
+    </row>
+    <row r="30" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B30" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="12"/>
+    </row>
+    <row r="32" spans="2:7" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="14"/>
+    </row>
+    <row r="33" spans="2:7" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="B33" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="F33" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="14"/>
+    </row>
+    <row r="35" spans="2:7" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="B35" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="F35" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="14"/>
+    </row>
+    <row r="37" spans="2:7" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E39" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="F39" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="14"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="14"/>
+    </row>
+    <row r="41" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B41" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E41" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="F41" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="G41" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B42" s="12"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
+      <c r="G42" s="12"/>
+    </row>
+    <row r="43" spans="2:7" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="14"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E43" s="17"/>
+      <c r="F43" s="17"/>
+      <c r="G43" s="14"/>
+    </row>
+    <row r="44" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B44" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E44" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F44" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G44" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B45" s="14"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E45" s="17"/>
+      <c r="F45" s="17"/>
+      <c r="G45" s="14"/>
+    </row>
+    <row r="46" spans="2:7" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B47" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E47" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="F47" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="G47" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B48" s="12"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E48" s="16"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="12"/>
+    </row>
+    <row r="49" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B49" s="12"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E49" s="16"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="12"/>
+    </row>
+    <row r="50" spans="2:7" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B50" s="14"/>
+      <c r="C50" s="14"/>
+      <c r="D50" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E50" s="17"/>
+      <c r="F50" s="17"/>
+      <c r="G50" s="14"/>
+    </row>
+    <row r="51" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B51" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E51" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="F51" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="G51" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B52" s="12"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E52" s="16"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="12"/>
+    </row>
+    <row r="53" spans="2:7" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="14"/>
+      <c r="C53" s="14"/>
+      <c r="D53" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E53" s="17"/>
+      <c r="F53" s="17"/>
+      <c r="G53" s="14"/>
+    </row>
+    <row r="54" spans="2:7" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="B54" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E54" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="F54" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="G54" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B55" s="14"/>
+      <c r="C55" s="14"/>
+      <c r="D55" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E55" s="17"/>
+      <c r="F55" s="17"/>
+      <c r="G55" s="14"/>
+    </row>
+    <row r="56" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B56" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="C56" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E56" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="F56" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="G56" s="13" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B57" s="14"/>
+      <c r="C57" s="14"/>
+      <c r="D57" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="E57" s="17"/>
+      <c r="F57" s="17"/>
+      <c r="G57" s="14"/>
+    </row>
+    <row r="58" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B58" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E58" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="F58" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="G58" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B59" s="12"/>
+      <c r="C59" s="12"/>
+      <c r="D59" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E59" s="16"/>
+      <c r="F59" s="16"/>
+      <c r="G59" s="12"/>
+    </row>
+    <row r="60" spans="2:7" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="14"/>
+      <c r="C60" s="14"/>
+      <c r="D60" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E60" s="17"/>
+      <c r="F60" s="17"/>
+      <c r="G60" s="14"/>
+    </row>
+    <row r="61" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B61" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="C61" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E61" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="F61" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="G61" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B62" s="12"/>
+      <c r="C62" s="12"/>
+      <c r="D62" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="E62" s="16"/>
+      <c r="F62" s="16"/>
+      <c r="G62" s="12"/>
+    </row>
+    <row r="63" spans="2:7" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="14"/>
+      <c r="C63" s="14"/>
+      <c r="D63" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="E63" s="17"/>
+      <c r="F63" s="17"/>
+      <c r="G63" s="14"/>
+    </row>
+    <row r="64" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B64" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="C64" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E64" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="F64" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="G64" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B65" s="12"/>
+      <c r="C65" s="12"/>
+      <c r="D65" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E65" s="16"/>
+      <c r="F65" s="16"/>
+      <c r="G65" s="12"/>
+    </row>
+    <row r="66" spans="2:7" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B66" s="14"/>
+      <c r="C66" s="14"/>
+      <c r="D66" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E66" s="17"/>
+      <c r="F66" s="17"/>
+      <c r="G66" s="14"/>
+    </row>
+    <row r="67" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B67" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="C67" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E67" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="F67" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="G67" s="13" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="68" spans="2:7" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B68" s="14"/>
+      <c r="C68" s="14"/>
+      <c r="D68" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="E68" s="17"/>
+      <c r="F68" s="17"/>
+      <c r="G68" s="14"/>
+    </row>
+    <row r="69" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B69" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="C69" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E69" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="F69" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="G69" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="70" spans="2:7" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B70" s="14"/>
+      <c r="C70" s="14"/>
+      <c r="D70" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="E70" s="17"/>
+      <c r="F70" s="17"/>
+      <c r="G70" s="14"/>
+    </row>
+    <row r="71" spans="2:7" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="G71" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="72" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B72" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="C72" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E72" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="F72" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="G72" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B73" s="12"/>
+      <c r="C73" s="12"/>
+      <c r="D73" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E73" s="16"/>
+      <c r="F73" s="16"/>
+      <c r="G73" s="12"/>
+    </row>
+    <row r="74" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B74" s="12"/>
+      <c r="C74" s="12"/>
+      <c r="D74" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E74" s="16"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="12"/>
+    </row>
+    <row r="75" spans="2:7" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B75" s="14"/>
+      <c r="C75" s="14"/>
+      <c r="D75" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E75" s="17"/>
+      <c r="F75" s="17"/>
+      <c r="G75" s="14"/>
+    </row>
+    <row r="76" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B76" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="C76" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E76" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="F76" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="G76" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B77" s="12"/>
+      <c r="C77" s="12"/>
+      <c r="D77" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E77" s="16"/>
+      <c r="F77" s="16"/>
+      <c r="G77" s="12"/>
+    </row>
+    <row r="78" spans="2:7" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B78" s="14"/>
+      <c r="C78" s="14"/>
+      <c r="D78" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="E78" s="17"/>
+      <c r="F78" s="17"/>
+      <c r="G78" s="14"/>
+    </row>
+    <row r="79" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B79" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="C79" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="E79" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="F79" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="G79" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="80" spans="2:7" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B80" s="14"/>
+      <c r="C80" s="14"/>
+      <c r="D80" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="E80" s="17"/>
+      <c r="F80" s="17"/>
+      <c r="G80" s="14"/>
+    </row>
+    <row r="81" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B81" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="C81" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E81" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="F81" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="G81" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="82" spans="2:7" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B82" s="14"/>
+      <c r="C82" s="14"/>
+      <c r="D82" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="E82" s="17"/>
+      <c r="F82" s="17"/>
+      <c r="G82" s="14"/>
+    </row>
+    <row r="83" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B83" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="C83" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E83" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="F83" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="G83" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" spans="2:7" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B84" s="14"/>
+      <c r="C84" s="14"/>
+      <c r="D84" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="E84" s="17"/>
+      <c r="F84" s="17"/>
+      <c r="G84" s="14"/>
+    </row>
+    <row r="85" spans="2:7" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B85" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="G85" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="86" spans="2:7" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B86" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="G86" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="87" spans="2:7" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B87" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="G87" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="88" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B88" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="C88" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E88" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="F88" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="G88" s="13" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="89" spans="2:7" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B89" s="14"/>
+      <c r="C89" s="14"/>
+      <c r="D89" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="E89" s="17"/>
+      <c r="F89" s="17"/>
+      <c r="G89" s="14"/>
+    </row>
+    <row r="90" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B90" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="C90" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E90" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="F90" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="G90" s="13" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="91" spans="2:7" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B91" s="14"/>
+      <c r="C91" s="14"/>
+      <c r="D91" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="E91" s="17"/>
+      <c r="F91" s="17"/>
+      <c r="G91" s="14"/>
+    </row>
+    <row r="92" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B92" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="C92" s="13" t="s">
+        <v>241</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="E92" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="F92" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="G92" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="93" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B93" s="12"/>
+      <c r="C93" s="12"/>
+      <c r="D93" s="7"/>
+      <c r="E93" s="16"/>
+      <c r="F93" s="16"/>
+      <c r="G93" s="12"/>
+    </row>
+    <row r="94" spans="2:7" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B94" s="14"/>
+      <c r="C94" s="14"/>
+      <c r="D94" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="E94" s="17"/>
+      <c r="F94" s="17"/>
+      <c r="G94" s="14"/>
+    </row>
+    <row r="95" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B95" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="C95" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E95" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="F95" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="G95" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="96" spans="2:7" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B96" s="14"/>
+      <c r="C96" s="14"/>
+      <c r="D96" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E96" s="17"/>
+      <c r="F96" s="17"/>
+      <c r="G96" s="14"/>
+    </row>
+    <row r="97" spans="2:7" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B97" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="G97" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="98" spans="2:7" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B98" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="G98" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="99" spans="2:7" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B99" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="G99" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="100" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B100" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="C100" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E100" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="F100" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="G100" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="2:7" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B101" s="14"/>
+      <c r="C101" s="14"/>
+      <c r="D101" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="E101" s="17"/>
+      <c r="F101" s="17"/>
+      <c r="G101" s="14"/>
+    </row>
+    <row r="102" spans="2:7" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B102" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="E102" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="G102" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="103" spans="2:7" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B103" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="E103" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="G103" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="104" spans="2:7" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="B104" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="C104" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="E104" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="F104" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="G104" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="105" spans="2:7" ht="24" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B105" s="14"/>
+      <c r="C105" s="14"/>
+      <c r="D105" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="E105" s="17"/>
+      <c r="F105" s="17"/>
+      <c r="G105" s="14"/>
+    </row>
+    <row r="106" spans="2:7" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B106" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="F106" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="G106" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="174">
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="E104:E105"/>
+    <mergeCell ref="F104:F105"/>
+    <mergeCell ref="G104:G105"/>
+    <mergeCell ref="B95:B96"/>
+    <mergeCell ref="C95:C96"/>
+    <mergeCell ref="E95:E96"/>
+    <mergeCell ref="F95:F96"/>
+    <mergeCell ref="G95:G96"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="C100:C101"/>
+    <mergeCell ref="E100:E101"/>
+    <mergeCell ref="F100:F101"/>
+    <mergeCell ref="G100:G101"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="C90:C91"/>
+    <mergeCell ref="E90:E91"/>
+    <mergeCell ref="F90:F91"/>
+    <mergeCell ref="G90:G91"/>
+    <mergeCell ref="B92:B94"/>
+    <mergeCell ref="C92:C94"/>
+    <mergeCell ref="E92:E94"/>
+    <mergeCell ref="F92:F94"/>
+    <mergeCell ref="G92:G94"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="C83:C84"/>
+    <mergeCell ref="E83:E84"/>
+    <mergeCell ref="F83:F84"/>
+    <mergeCell ref="G83:G84"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="C88:C89"/>
+    <mergeCell ref="E88:E89"/>
+    <mergeCell ref="F88:F89"/>
+    <mergeCell ref="G88:G89"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="C79:C80"/>
+    <mergeCell ref="E79:E80"/>
+    <mergeCell ref="F79:F80"/>
+    <mergeCell ref="G79:G80"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="C81:C82"/>
+    <mergeCell ref="E81:E82"/>
+    <mergeCell ref="F81:F82"/>
+    <mergeCell ref="G81:G82"/>
+    <mergeCell ref="B72:B75"/>
+    <mergeCell ref="C72:C75"/>
+    <mergeCell ref="E72:E75"/>
+    <mergeCell ref="F72:F75"/>
+    <mergeCell ref="G72:G75"/>
+    <mergeCell ref="B76:B78"/>
+    <mergeCell ref="C76:C78"/>
+    <mergeCell ref="E76:E78"/>
+    <mergeCell ref="F76:F78"/>
+    <mergeCell ref="G76:G78"/>
+    <mergeCell ref="B67:B68"/>
+    <mergeCell ref="C67:C68"/>
+    <mergeCell ref="E67:E68"/>
+    <mergeCell ref="F67:F68"/>
+    <mergeCell ref="G67:G68"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="C69:C70"/>
+    <mergeCell ref="E69:E70"/>
+    <mergeCell ref="F69:F70"/>
+    <mergeCell ref="G69:G70"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="C61:C63"/>
+    <mergeCell ref="E61:E63"/>
+    <mergeCell ref="F61:F63"/>
+    <mergeCell ref="G61:G63"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="C64:C66"/>
+    <mergeCell ref="E64:E66"/>
+    <mergeCell ref="F64:F66"/>
+    <mergeCell ref="G64:G66"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="E56:E57"/>
+    <mergeCell ref="F56:F57"/>
+    <mergeCell ref="G56:G57"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="C58:C60"/>
+    <mergeCell ref="E58:E60"/>
+    <mergeCell ref="F58:F60"/>
+    <mergeCell ref="G58:G60"/>
+    <mergeCell ref="B51:B53"/>
+    <mergeCell ref="C51:C53"/>
+    <mergeCell ref="E51:E53"/>
+    <mergeCell ref="F51:F53"/>
+    <mergeCell ref="G51:G53"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="F54:F55"/>
+    <mergeCell ref="G54:G55"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="B47:B50"/>
+    <mergeCell ref="C47:C50"/>
+    <mergeCell ref="E47:E50"/>
+    <mergeCell ref="F47:F50"/>
+    <mergeCell ref="G47:G50"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="G39:G40"/>
+    <mergeCell ref="B41:B43"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="E41:E43"/>
+    <mergeCell ref="F41:F43"/>
+    <mergeCell ref="G41:G43"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="G33:G34"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="C26:C29"/>
+    <mergeCell ref="E26:E29"/>
+    <mergeCell ref="F26:F29"/>
+    <mergeCell ref="G26:G29"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="E30:E32"/>
+    <mergeCell ref="F30:F32"/>
+    <mergeCell ref="G30:G32"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="E8:E11"/>
+    <mergeCell ref="F8:F11"/>
+    <mergeCell ref="G8:G11"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="G12:G14"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="C4:C7"/>
+    <mergeCell ref="E4:E7"/>
+    <mergeCell ref="F4:F7"/>
+    <mergeCell ref="G4:G7"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>